--- a/DateBase/orders/Nha Thu_2026-8-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-19.xlsx
@@ -1279,6 +1279,9 @@
       <c r="G2" t="str">
         <v>01010555510101010515510101010555555555510101015912551055510551515555515105151055109355101010910104110309105555551058575151510520105</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
